--- a/Output Files GPT-OSS 20B/Example-Guided_LLM_Scoring_results_stats.xlsx
+++ b/Output Files GPT-OSS 20B/Example-Guided_LLM_Scoring_results_stats.xlsx
@@ -523,16 +523,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="E2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.8</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.9</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>0.8</v>
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F4" t="n">
         <v>0.8</v>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9</v>
       </c>
       <c r="F5" t="n">
         <v>0.8</v>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.7</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -878,16 +878,16 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.9</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.7</v>
-      </c>
       <c r="F7" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>0.8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F8" t="n">
         <v>0.9</v>
@@ -1171,7 +1171,7 @@
         <v>0.6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1304,13 +1304,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F13" t="n">
         <v>0.8</v>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E14" t="n">
         <v>0.9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.7</v>
       </c>
       <c r="F14" t="n">
         <v>0.9</v>
@@ -1446,16 +1446,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1517,16 +1517,16 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E16" t="n">
         <v>0.7</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.5</v>
-      </c>
       <c r="F16" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1588,16 +1588,16 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D17" t="n">
         <v>0.8</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.9</v>
-      </c>
       <c r="E17" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1659,16 +1659,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1801,16 +1801,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D20" t="n">
         <v>0.8</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1872,13 +1872,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F21" t="n">
         <v>0.8</v>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F22" t="n">
         <v>0.7</v>
@@ -2085,13 +2085,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="D24" t="n">
         <v>0.9</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="F24" t="n">
         <v>0.9</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E25" t="n">
         <v>0.8</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.5</v>
       </c>
       <c r="F25" t="n">
         <v>0.8</v>
@@ -2369,16 +2369,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="D28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E28" t="n">
         <v>0.9</v>
       </c>
-      <c r="E28" t="n">
-        <v>0.8</v>
-      </c>
       <c r="F28" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2440,13 +2440,13 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E29" t="n">
         <v>0.9</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.8</v>
       </c>
       <c r="F29" t="n">
         <v>0.9</v>
@@ -2511,16 +2511,16 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E30" t="n">
         <v>0.7</v>
       </c>
-      <c r="D30" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.9</v>
-      </c>
       <c r="F30" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>0.5</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="E32" t="n">
         <v>0.9</v>
@@ -2724,16 +2724,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D33" t="n">
         <v>0.8</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>0.8</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F34" t="n">
         <v>0.8</v>
@@ -2866,16 +2866,16 @@
         </is>
       </c>
       <c r="C35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E35" t="n">
         <v>0.5</v>
       </c>
-      <c r="D35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.6</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E36" t="n">
         <v>0.9</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3008,13 +3008,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F37" t="n">
         <v>0.6</v>
@@ -3079,13 +3079,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="D38" t="n">
         <v>0.5</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F38" t="n">
         <v>0.8</v>
@@ -3150,16 +3150,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D39" t="n">
         <v>0.5</v>
       </c>
       <c r="E39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F39" t="n">
         <v>0.8</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.7</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3221,13 +3221,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F40" t="n">
         <v>0.8</v>
@@ -3292,16 +3292,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E41" t="n">
         <v>0.9</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="D42" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
         <v>0.9</v>
@@ -3434,16 +3434,16 @@
         </is>
       </c>
       <c r="C43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F43" t="n">
         <v>0.95</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.9</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3505,16 +3505,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D44" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E44" t="n">
         <v>0.6</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3576,13 +3576,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D45" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F45" t="n">
         <v>0.8</v>
@@ -3647,16 +3647,16 @@
         </is>
       </c>
       <c r="C46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E46" t="n">
         <v>0.8</v>
       </c>
-      <c r="D46" t="n">
+      <c r="F46" t="n">
         <v>0.8</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.7</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3718,16 +3718,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D47" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E47" t="n">
         <v>0.6</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="E48" t="n">
         <v>0.9</v>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D49" t="n">
         <v>0.5</v>
@@ -3869,7 +3869,7 @@
         <v>0.9</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3931,16 +3931,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D50" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E50" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F50" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>0.7</v>
       </c>
       <c r="E51" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F51" t="n">
         <v>0.9</v>
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D52" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E52" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="F52" t="n">
         <v>0.9</v>
@@ -4144,16 +4144,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E53" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -4215,16 +4215,16 @@
         </is>
       </c>
       <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F54" t="n">
         <v>0.8</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.5</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -4292,10 +4292,10 @@
         <v>0.2</v>
       </c>
       <c r="E55" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -4357,13 +4357,13 @@
         </is>
       </c>
       <c r="C56" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E56" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.7</v>
       </c>
       <c r="F56" t="n">
         <v>0.8</v>
@@ -4428,16 +4428,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D57" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E57" t="n">
         <v>0.9</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -4499,13 +4499,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="D58" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="F58" t="n">
         <v>0.9</v>
@@ -4576,10 +4576,10 @@
         <v>0.8</v>
       </c>
       <c r="E59" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F59" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.6</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -4647,10 +4647,10 @@
         <v>0.7</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -4712,16 +4712,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D61" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E61" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4783,16 +4783,16 @@
         </is>
       </c>
       <c r="C62" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E62" t="n">
         <v>0.6</v>
       </c>
-      <c r="D62" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.5</v>
-      </c>
       <c r="F62" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4854,16 +4854,16 @@
         </is>
       </c>
       <c r="C63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F63" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.7</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>0.8</v>
       </c>
       <c r="F64" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D65" t="n">
         <v>0.6</v>
@@ -5073,7 +5073,7 @@
         <v>0.6</v>
       </c>
       <c r="E66" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="F66" t="n">
         <v>0.8</v>
@@ -5138,16 +5138,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D67" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E67" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -5209,16 +5209,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D68" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E68" t="n">
         <v>0.7</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>0.6</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F69" t="n">
         <v>0.7</v>
@@ -5351,13 +5351,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="D70" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="F70" t="n">
         <v>0.6</v>
@@ -5422,13 +5422,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D71" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E71" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="F71" t="n">
         <v>0.8</v>
@@ -5493,16 +5493,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D72" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E72" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F72" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>0.4</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -5635,13 +5635,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="D74" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="E74" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
         <v>0.8</v>
@@ -5706,13 +5706,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D75" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F75" t="n">
         <v>0.8</v>
@@ -5777,13 +5777,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="D76" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="E76" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F76" t="n">
         <v>0.8</v>
@@ -5854,7 +5854,7 @@
         <v>0.4</v>
       </c>
       <c r="E77" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F77" t="n">
         <v>0.6</v>
@@ -5919,16 +5919,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E78" t="n">
         <v>0.8</v>
       </c>
       <c r="F78" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D79" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E79" t="n">
         <v>0.8</v>
@@ -6061,16 +6061,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="D80" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="E80" t="n">
         <v>0.7</v>
       </c>
       <c r="F80" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -6203,10 +6203,10 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="D82" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E82" t="n">
         <v>0.9</v>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D83" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E83" t="n">
         <v>0.8</v>
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D84" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="E84" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="F84" t="n">
         <v>0.8</v>
@@ -6416,16 +6416,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D85" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E85" t="n">
         <v>0.8</v>
       </c>
       <c r="F85" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -6487,13 +6487,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D86" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="E86" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F86" t="n">
         <v>0.8</v>
@@ -6558,16 +6558,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="D87" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E87" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F87" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -6629,16 +6629,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="D88" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="E88" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="F88" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D89" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E89" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="F89" t="n">
         <v>0.8</v>
@@ -6771,16 +6771,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="D90" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="E90" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="F90" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -6913,10 +6913,10 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D92" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E92" t="n">
         <v>0.6</v>
@@ -6984,16 +6984,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="D93" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="E93" t="n">
         <v>0.9</v>
       </c>
       <c r="F93" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>0.8</v>
       </c>
       <c r="E94" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F94" t="n">
         <v>0.8</v>
@@ -7197,13 +7197,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D96" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E96" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F96" t="n">
         <v>0.9</v>
@@ -7268,13 +7268,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="D97" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E97" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
         <v>0.8</v>
@@ -7410,13 +7410,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="D99" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="E99" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F99" t="n">
         <v>0.8</v>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E100" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F100" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0.8</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="D101" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="E101" t="n">
         <v>0.9</v>
@@ -7623,16 +7623,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="D102" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="E102" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F102" t="n">
         <v>0.8</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0.9</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -7694,13 +7694,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="D103" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="E103" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="F103" t="n">
         <v>0.8</v>
@@ -7771,10 +7771,10 @@
         <v>0.2</v>
       </c>
       <c r="E104" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -7836,16 +7836,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D105" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E105" t="n">
         <v>0.3</v>
       </c>
       <c r="F105" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -7913,10 +7913,10 @@
         <v>0.6</v>
       </c>
       <c r="E106" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F106" t="n">
         <v>0.8</v>
-      </c>
-      <c r="F106" t="n">
-        <v>0.7</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>0.8</v>
       </c>
       <c r="F107" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -8049,10 +8049,10 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D108" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E108" t="n">
         <v>1</v>
@@ -8126,7 +8126,7 @@
         <v>0.6</v>
       </c>
       <c r="E109" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="F109" t="n">
         <v>0.8</v>
@@ -8191,13 +8191,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D110" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E110" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F110" t="n">
         <v>0.9</v>
@@ -8262,16 +8262,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="D111" t="n">
         <v>0.6</v>
       </c>
       <c r="E111" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F111" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -8333,16 +8333,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="D112" t="n">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="E112" t="n">
         <v>0.7</v>
       </c>
       <c r="F112" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -8404,10 +8404,10 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E113" t="n">
         <v>0.6</v>
@@ -8475,16 +8475,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="D114" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E114" t="n">
         <v>0.8</v>
       </c>
       <c r="F114" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -8617,16 +8617,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F116" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -8759,16 +8759,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F118" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -8830,13 +8830,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="D119" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="E119" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="F119" t="n">
         <v>0.6</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="D120" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="E120" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F120" t="n">
         <v>0.7</v>
@@ -8978,10 +8978,10 @@
         <v>0.8</v>
       </c>
       <c r="E121" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F121" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F121" t="n">
-        <v>0.8</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -9043,16 +9043,16 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D122" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E122" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F122" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -9114,13 +9114,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="D123" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="E123" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F123" t="n">
         <v>0.8</v>
@@ -9185,13 +9185,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="D124" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="E124" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="F124" t="n">
         <v>0.8</v>
@@ -9262,7 +9262,7 @@
         <v>0.9</v>
       </c>
       <c r="E125" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F125" t="n">
         <v>0.7</v>
@@ -9333,7 +9333,7 @@
         <v>0.9</v>
       </c>
       <c r="E126" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F126" t="n">
         <v>0.7</v>
@@ -9398,13 +9398,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D127" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E127" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F127" t="n">
         <v>0.8</v>
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="D128" t="n">
         <v>0.6</v>
       </c>
       <c r="E128" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F128" t="n">
         <v>0.8</v>
@@ -9540,16 +9540,16 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D129" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E129" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="F129" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -9617,10 +9617,10 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -9682,13 +9682,13 @@
         </is>
       </c>
       <c r="C131" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E131" t="n">
         <v>0.7</v>
-      </c>
-      <c r="D131" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E131" t="n">
-        <v>0.5</v>
       </c>
       <c r="F131" t="n">
         <v>0.8</v>
@@ -9753,16 +9753,16 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D132" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E132" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F132" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>0.2</v>
       </c>
       <c r="F133" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -9895,16 +9895,16 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="D134" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E134" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F134" t="n">
         <v>0.8</v>
-      </c>
-      <c r="F134" t="n">
-        <v>0.9</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -9966,16 +9966,16 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D135" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E135" t="n">
         <v>0.9</v>
       </c>
       <c r="F135" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>0.7</v>
       </c>
       <c r="F136" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -10250,13 +10250,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="D139" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="E139" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F139" t="n">
         <v>0.7</v>
@@ -10321,10 +10321,10 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D140" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E140" t="n">
         <v>0.7</v>
@@ -10392,16 +10392,16 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="D141" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E141" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F141" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -10463,13 +10463,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="D142" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E142" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="F142" t="n">
         <v>0.7</v>
@@ -10540,10 +10540,10 @@
         <v>0.8</v>
       </c>
       <c r="E143" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F143" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -10605,16 +10605,16 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="D144" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="E144" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F144" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -10676,16 +10676,16 @@
         </is>
       </c>
       <c r="C145" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F145" t="n">
         <v>0.7</v>
-      </c>
-      <c r="D145" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E145" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F145" t="n">
-        <v>0.9</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -10747,16 +10747,16 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="D146" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="E146" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F146" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>0.9</v>
       </c>
       <c r="F147" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -11031,13 +11031,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="D150" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E150" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F150" t="n">
         <v>0.8</v>
@@ -11108,7 +11108,7 @@
         <v>0.3</v>
       </c>
       <c r="E151" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F151" t="n">
         <v>0.8</v>
@@ -11173,16 +11173,16 @@
         </is>
       </c>
       <c r="C152" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E152" t="n">
         <v>0.8</v>
       </c>
-      <c r="D152" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E152" t="n">
-        <v>0.7</v>
-      </c>
       <c r="F152" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -11244,16 +11244,16 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="D153" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E153" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F153" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F153" t="n">
-        <v>0.8</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -11315,16 +11315,16 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D154" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E154" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F154" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -11386,13 +11386,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="D155" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E155" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="F155" t="n">
         <v>0.8</v>
@@ -11457,16 +11457,16 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="D156" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E156" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F156" t="n">
         <v>0.8</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0.9</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -11534,10 +11534,10 @@
         <v>0.6</v>
       </c>
       <c r="E157" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F157" t="n">
         <v>0.8</v>
-      </c>
-      <c r="F157" t="n">
-        <v>0.9</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>0.8</v>
       </c>
       <c r="E158" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F158" t="n">
         <v>0.6</v>
@@ -11679,7 +11679,7 @@
         <v>0.7</v>
       </c>
       <c r="F159" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -11741,16 +11741,16 @@
         </is>
       </c>
       <c r="C160" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F160" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D160" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E160" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F160" t="n">
-        <v>0.8</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -11812,13 +11812,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F161" t="n">
         <v>0.8</v>
@@ -11889,7 +11889,7 @@
         <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="F162" t="n">
         <v>0.9</v>
@@ -11954,13 +11954,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E163" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F163" t="n">
         <v>0.8</v>
@@ -12025,16 +12025,16 @@
         </is>
       </c>
       <c r="C164" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F164" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D164" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E164" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F164" t="n">
-        <v>0.8</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -12096,16 +12096,16 @@
         </is>
       </c>
       <c r="C165" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E165" t="n">
         <v>0.7</v>
       </c>
-      <c r="D165" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E165" t="n">
-        <v>0.5</v>
-      </c>
       <c r="F165" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -12167,16 +12167,16 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D166" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E166" t="n">
         <v>0.8</v>
       </c>
       <c r="F166" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -12238,10 +12238,10 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D167" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E167" t="n">
         <v>0.8</v>
@@ -12309,13 +12309,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="D168" t="n">
         <v>0.8</v>
       </c>
       <c r="E168" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F168" t="n">
         <v>0.9</v>
@@ -12380,16 +12380,16 @@
         </is>
       </c>
       <c r="C169" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F169" t="n">
         <v>0.9</v>
-      </c>
-      <c r="D169" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E169" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F169" t="n">
-        <v>0.8</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -12451,10 +12451,10 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D170" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E170" t="n">
         <v>0.8</v>
@@ -12522,16 +12522,16 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="D171" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="E171" t="n">
         <v>0.95</v>
       </c>
       <c r="F171" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -12599,10 +12599,10 @@
         <v>0.6</v>
       </c>
       <c r="E172" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="F172" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -12664,16 +12664,16 @@
         </is>
       </c>
       <c r="C173" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F173" t="n">
         <v>0.7</v>
-      </c>
-      <c r="D173" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E173" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F173" t="n">
-        <v>0.6</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -12741,10 +12741,10 @@
         <v>0.5</v>
       </c>
       <c r="E174" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F174" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -12806,16 +12806,16 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D175" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E175" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F175" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -12877,16 +12877,16 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D176" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E176" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F176" t="n">
         <v>0.4</v>
-      </c>
-      <c r="F176" t="n">
-        <v>0.6</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -13019,10 +13019,10 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D178" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E178" t="n">
         <v>0.9</v>
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="D179" t="n">
         <v>0.7</v>
@@ -13161,16 +13161,16 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="D180" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="E180" t="n">
         <v>0.9</v>
       </c>
       <c r="F180" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -13232,16 +13232,16 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D181" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E181" t="n">
         <v>0.9</v>
       </c>
       <c r="F181" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -13309,10 +13309,10 @@
         <v>0.8</v>
       </c>
       <c r="E182" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F182" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F182" t="n">
-        <v>0.6</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -13374,16 +13374,16 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D183" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E183" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F183" t="n">
         <v>0.8</v>
-      </c>
-      <c r="F183" t="n">
-        <v>0.7</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -13516,13 +13516,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="D185" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="E185" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="F185" t="n">
         <v>0.6</v>
@@ -13729,16 +13729,16 @@
         </is>
       </c>
       <c r="C188" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E188" t="n">
         <v>0.8</v>
       </c>
-      <c r="D188" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E188" t="n">
+      <c r="F188" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F188" t="n">
-        <v>0.8</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -13803,13 +13803,13 @@
         <v>0.8</v>
       </c>
       <c r="D189" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="E189" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F189" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F189" t="n">
-        <v>0.75</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>0.5</v>
       </c>
       <c r="F190" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>1</v>
       </c>
       <c r="E191" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F191" t="n">
         <v>0.8</v>
@@ -14013,7 +14013,7 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="D192" t="n">
         <v>0.9</v>
@@ -14155,16 +14155,16 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D194" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" t="n">
         <v>0.3</v>
-      </c>
-      <c r="F194" t="n">
-        <v>0.7</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -14226,13 +14226,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="D195" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="E195" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="F195" t="n">
         <v>0.6</v>
@@ -14297,16 +14297,16 @@
         </is>
       </c>
       <c r="C196" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E196" t="n">
         <v>0.5</v>
       </c>
-      <c r="D196" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E196" t="n">
-        <v>0.8</v>
-      </c>
       <c r="F196" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -14368,16 +14368,16 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E197" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F197" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -14442,10 +14442,10 @@
         <v>0.8</v>
       </c>
       <c r="D198" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E198" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F198" t="n">
         <v>0.8</v>
@@ -14510,13 +14510,13 @@
         </is>
       </c>
       <c r="C199" t="n">
+        <v>1</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" t="n">
         <v>0.9</v>
-      </c>
-      <c r="D199" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E199" t="n">
-        <v>0.8</v>
       </c>
       <c r="F199" t="n">
         <v>0.8</v>
@@ -14794,16 +14794,16 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D203" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E203" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F203" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F203" t="n">
-        <v>0.6</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -14865,16 +14865,16 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D204" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E204" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F204" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D205" t="n">
         <v>0.5</v>
@@ -15007,13 +15007,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="D206" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E206" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F206" t="n">
         <v>0.8</v>
@@ -15078,13 +15078,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="D207" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="E207" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="F207" t="n">
         <v>0.8</v>
@@ -15149,13 +15149,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D208" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E208" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F208" t="n">
         <v>0.8</v>
@@ -15220,10 +15220,10 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D209" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E209" t="n">
         <v>0.8</v>
@@ -15297,10 +15297,10 @@
         <v>0.6</v>
       </c>
       <c r="E210" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F210" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -15362,16 +15362,16 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="D211" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E211" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F211" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -15433,16 +15433,16 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D212" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="E212" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F212" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>0.3</v>
       </c>
       <c r="F213" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>0.9</v>
       </c>
       <c r="E214" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F214" t="n">
         <v>0.3</v>
@@ -15652,7 +15652,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D215" t="n">
         <v>0.2</v>
@@ -15725,7 +15725,7 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D216" t="n">
         <v>0.3</v>
@@ -15734,7 +15734,7 @@
         <v>1</v>
       </c>
       <c r="F216" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -15798,16 +15798,16 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="D217" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E217" t="n">
-        <v>0.9</v>
+        <v>0.55</v>
       </c>
       <c r="F217" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -15871,13 +15871,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D218" t="n">
         <v>0.7</v>
       </c>
       <c r="E218" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F218" t="n">
         <v>0.6</v>
@@ -15944,16 +15944,16 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="D219" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="E219" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F219" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -16017,13 +16017,13 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="D220" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F220" t="n">
         <v>0.8</v>
@@ -16236,16 +16236,16 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D223" t="n">
         <v>1</v>
       </c>
       <c r="E223" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F223" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -16312,13 +16312,13 @@
         <v>0.4</v>
       </c>
       <c r="D224" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E224" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="F224" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D225" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="E225" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F225" t="n">
         <v>0.9</v>
@@ -16534,10 +16534,10 @@
         <v>1</v>
       </c>
       <c r="E227" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="F227" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -16601,16 +16601,16 @@
         </is>
       </c>
       <c r="C228" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E228" t="n">
         <v>0.8</v>
       </c>
-      <c r="D228" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E228" t="n">
-        <v>0.6</v>
-      </c>
       <c r="F228" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -16674,16 +16674,16 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D229" t="n">
         <v>1</v>
       </c>
       <c r="E229" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F229" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -16747,16 +16747,16 @@
         </is>
       </c>
       <c r="C230" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E230" t="n">
         <v>0.5</v>
       </c>
-      <c r="D230" t="n">
-        <v>0</v>
-      </c>
-      <c r="E230" t="n">
-        <v>0.2</v>
-      </c>
       <c r="F230" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -16820,16 +16820,16 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D231" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E231" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F231" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -16972,10 +16972,10 @@
         <v>0.8</v>
       </c>
       <c r="E233" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F233" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -17112,10 +17112,10 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D235" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E235" t="n">
         <v>1</v>
@@ -17185,13 +17185,13 @@
         </is>
       </c>
       <c r="C236" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D236" t="n">
         <v>0.2</v>
       </c>
-      <c r="D236" t="n">
-        <v>0.1</v>
-      </c>
       <c r="E236" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F236" t="n">
         <v>0.3</v>
@@ -17258,16 +17258,16 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="D237" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F237" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -17331,16 +17331,16 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D238" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E238" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F238" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -17404,16 +17404,16 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D239" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E239" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F239" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -17477,16 +17477,16 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D240" t="n">
         <v>0.8</v>
       </c>
       <c r="E240" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F240" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -17550,16 +17550,16 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="D241" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="E241" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F241" t="n">
         <v>0.4</v>
-      </c>
-      <c r="F241" t="n">
-        <v>0.5</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -17623,16 +17623,16 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="D242" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F242" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E242" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F242" t="n">
-        <v>0.3</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -17696,16 +17696,16 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="D243" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E243" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="F243" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>0.4</v>
       </c>
       <c r="E244" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F244" t="n">
         <v>0.8</v>
@@ -17848,10 +17848,10 @@
         <v>1</v>
       </c>
       <c r="E245" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F245" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -17921,10 +17921,10 @@
         <v>1</v>
       </c>
       <c r="E246" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F246" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -17988,13 +17988,13 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D247" t="n">
         <v>1</v>
       </c>
       <c r="E247" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F247" t="n">
         <v>0.7</v>
@@ -18064,13 +18064,13 @@
         <v>0.8</v>
       </c>
       <c r="D248" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="E248" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F248" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -18134,13 +18134,13 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="D249" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E249" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="F249" t="n">
         <v>0.9</v>
@@ -18207,16 +18207,16 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D250" t="n">
         <v>0.2</v>
       </c>
       <c r="E250" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F250" t="n">
         <v>0.4</v>
-      </c>
-      <c r="F250" t="n">
-        <v>0.3</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -18283,13 +18283,13 @@
         <v>0.8</v>
       </c>
       <c r="D251" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E251" t="n">
         <v>0.2</v>
       </c>
-      <c r="E251" t="n">
-        <v>0.3</v>
-      </c>
       <c r="F251" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D252" t="n">
         <v>0.1</v>
@@ -18426,10 +18426,10 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D253" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E253" t="n">
         <v>1</v>
@@ -18502,13 +18502,13 @@
         <v>0.9</v>
       </c>
       <c r="D254" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E254" t="n">
         <v>0.7</v>
       </c>
       <c r="F254" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -18572,16 +18572,16 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D255" t="n">
         <v>0.6</v>
       </c>
       <c r="E255" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F255" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="D256" t="n">
         <v>0.7</v>
@@ -18800,7 +18800,7 @@
         <v>0.6</v>
       </c>
       <c r="F258" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
@@ -18864,16 +18864,16 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D259" t="n">
         <v>0.9</v>
       </c>
       <c r="E259" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F259" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
@@ -18937,16 +18937,16 @@
         </is>
       </c>
       <c r="C260" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F260" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D260" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E260" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F260" t="n">
-        <v>0.7</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -19010,16 +19010,16 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D261" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E261" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F261" t="n">
         <v>0.6</v>
-      </c>
-      <c r="F261" t="n">
-        <v>0.9</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -19083,16 +19083,16 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D262" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E262" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="F262" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -19156,16 +19156,16 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="D263" t="n">
         <v>0.3</v>
       </c>
       <c r="E263" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F263" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
@@ -19229,13 +19229,13 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D264" t="n">
         <v>0.8</v>
       </c>
       <c r="E264" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F264" t="n">
         <v>0.3</v>
@@ -19302,7 +19302,7 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D265" t="n">
         <v>0.3</v>
@@ -19375,16 +19375,16 @@
         </is>
       </c>
       <c r="C266" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D266" t="n">
+        <v>1</v>
+      </c>
+      <c r="E266" t="n">
         <v>0.5</v>
       </c>
-      <c r="D266" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E266" t="n">
+      <c r="F266" t="n">
         <v>0.4</v>
-      </c>
-      <c r="F266" t="n">
-        <v>0.2</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
@@ -19451,13 +19451,13 @@
         <v>0.9</v>
       </c>
       <c r="D267" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E267" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F267" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
@@ -19521,16 +19521,16 @@
         </is>
       </c>
       <c r="C268" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D268" t="n">
+        <v>1</v>
+      </c>
+      <c r="E268" t="n">
         <v>0.8</v>
       </c>
-      <c r="D268" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E268" t="n">
-        <v>0.3</v>
-      </c>
       <c r="F268" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
@@ -19594,16 +19594,16 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="D269" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="E269" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="F269" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
@@ -19667,16 +19667,16 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D270" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E270" t="n">
         <v>1</v>
       </c>
       <c r="F270" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -19740,16 +19740,16 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D271" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E271" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F271" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -19819,10 +19819,10 @@
         <v>1</v>
       </c>
       <c r="E272" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F272" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -19886,16 +19886,16 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="D273" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="E273" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F273" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -20035,13 +20035,13 @@
         <v>0.8</v>
       </c>
       <c r="D275" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E275" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F275" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -20105,16 +20105,16 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D276" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="E276" t="n">
         <v>0.2</v>
       </c>
       <c r="F276" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -20181,13 +20181,13 @@
         <v>0.5</v>
       </c>
       <c r="D277" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E277" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F277" t="n">
         <v>0.8</v>
-      </c>
-      <c r="F277" t="n">
-        <v>0.7</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -20251,16 +20251,16 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="D278" t="n">
         <v>0.3</v>
       </c>
       <c r="E278" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F278" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -20324,16 +20324,16 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D279" t="n">
         <v>0.3</v>
       </c>
       <c r="E279" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F279" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D280" t="n">
         <v>0.3</v>
@@ -20473,13 +20473,13 @@
         <v>0.9</v>
       </c>
       <c r="D281" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E281" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="F281" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>0.3</v>
       </c>
       <c r="F282" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D283" t="n">
         <v>0.7</v>
@@ -20625,7 +20625,7 @@
         <v>1</v>
       </c>
       <c r="F283" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
@@ -20689,16 +20689,16 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D284" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="E284" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F284" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
@@ -20762,10 +20762,10 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D285" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E285" t="n">
         <v>1</v>
@@ -20981,16 +20981,16 @@
         </is>
       </c>
       <c r="C288" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E288" t="n">
         <v>0.9</v>
       </c>
-      <c r="D288" t="n">
-        <v>1</v>
-      </c>
-      <c r="E288" t="n">
-        <v>0.6</v>
-      </c>
       <c r="F288" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
@@ -21130,13 +21130,13 @@
         <v>0.9</v>
       </c>
       <c r="D290" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E290" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F290" t="n">
         <v>0.8</v>
-      </c>
-      <c r="E290" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F290" t="n">
-        <v>0.9</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
@@ -21273,16 +21273,16 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D292" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E292" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F292" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D293" t="n">
         <v>0.3</v>
@@ -21355,7 +21355,7 @@
         <v>0.8</v>
       </c>
       <c r="F293" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D294" t="n">
         <v>0.3</v>
@@ -21428,7 +21428,7 @@
         <v>0.6</v>
       </c>
       <c r="F294" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
@@ -21492,13 +21492,13 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D295" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E295" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F295" t="n">
         <v>0.5</v>
@@ -21571,10 +21571,10 @@
         <v>0.6</v>
       </c>
       <c r="E296" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F296" t="n">
         <v>0.8</v>
-      </c>
-      <c r="F296" t="n">
-        <v>0.6</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D297" t="n">
         <v>0.9</v>
@@ -21647,7 +21647,7 @@
         <v>0.4</v>
       </c>
       <c r="F297" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D298" t="n">
         <v>0.6</v>
@@ -21784,16 +21784,16 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="D299" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="E299" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="F299" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
@@ -21857,16 +21857,16 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="D300" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E300" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F300" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
@@ -21930,16 +21930,16 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D301" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E301" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F301" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -22003,13 +22003,13 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D302" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E302" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F302" t="n">
         <v>0.6</v>
@@ -22076,16 +22076,16 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D303" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E303" t="n">
         <v>0.2</v>
       </c>
       <c r="F303" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
@@ -22149,10 +22149,10 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D304" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E304" t="n">
         <v>0.9</v>
@@ -22222,16 +22222,16 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D305" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E305" t="n">
         <v>0.6</v>
       </c>
       <c r="F305" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
@@ -22298,10 +22298,10 @@
         <v>0.6</v>
       </c>
       <c r="D306" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E306" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F306" t="n">
         <v>0.9</v>
@@ -22371,10 +22371,10 @@
         <v>0.8</v>
       </c>
       <c r="D307" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E307" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F307" t="n">
         <v>0.9</v>
@@ -22444,10 +22444,10 @@
         <v>0.9</v>
       </c>
       <c r="D308" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E308" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F308" t="n">
         <v>0.5</v>
@@ -22520,10 +22520,10 @@
         <v>0.7</v>
       </c>
       <c r="E309" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F309" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -22666,10 +22666,10 @@
         <v>0.8</v>
       </c>
       <c r="E311" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F311" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
@@ -22733,13 +22733,13 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="D312" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E312" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F312" t="n">
         <v>0.6</v>
@@ -22812,7 +22812,7 @@
         <v>0.7</v>
       </c>
       <c r="E313" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F313" t="n">
         <v>0.3</v>
@@ -22879,16 +22879,16 @@
         </is>
       </c>
       <c r="C314" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E314" t="n">
         <v>0.8</v>
       </c>
-      <c r="D314" t="n">
+      <c r="F314" t="n">
         <v>0.7</v>
-      </c>
-      <c r="E314" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F314" t="n">
-        <v>0.8</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -22952,16 +22952,16 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="D315" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E315" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F315" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
@@ -23031,10 +23031,10 @@
         <v>0.4</v>
       </c>
       <c r="E316" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F316" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
@@ -23104,10 +23104,10 @@
         <v>1</v>
       </c>
       <c r="E317" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F317" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
@@ -23177,10 +23177,10 @@
         <v>1</v>
       </c>
       <c r="E318" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F318" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>0.6</v>
       </c>
       <c r="F319" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
@@ -23323,10 +23323,10 @@
         <v>0.9</v>
       </c>
       <c r="E320" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F320" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
@@ -23390,16 +23390,16 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D321" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E321" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F321" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
@@ -23536,10 +23536,10 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D323" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E323" t="n">
         <v>1</v>
@@ -23609,16 +23609,16 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D324" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E324" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F324" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
@@ -23755,13 +23755,13 @@
         </is>
       </c>
       <c r="C326" t="n">
+        <v>1</v>
+      </c>
+      <c r="D326" t="n">
+        <v>1</v>
+      </c>
+      <c r="E326" t="n">
         <v>0.8</v>
-      </c>
-      <c r="D326" t="n">
-        <v>1</v>
-      </c>
-      <c r="E326" t="n">
-        <v>0.6</v>
       </c>
       <c r="F326" t="n">
         <v>0.7</v>
@@ -23828,7 +23828,7 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D327" t="n">
         <v>1</v>
@@ -23974,16 +23974,16 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D329" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E329" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F329" t="n">
         <v>0.8</v>
-      </c>
-      <c r="F329" t="n">
-        <v>0.7</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D330" t="n">
         <v>0.1</v>
@@ -24056,7 +24056,7 @@
         <v>0.6</v>
       </c>
       <c r="F330" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>1</v>
       </c>
       <c r="F332" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
@@ -24266,7 +24266,7 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D333" t="n">
         <v>0.7</v>
@@ -24339,16 +24339,16 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D334" t="n">
         <v>0.7</v>
       </c>
       <c r="E334" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F334" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
@@ -24485,16 +24485,16 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D336" t="n">
         <v>0.3</v>
       </c>
       <c r="E336" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F336" t="n">
         <v>0.6</v>
-      </c>
-      <c r="F336" t="n">
-        <v>0.7</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>1</v>
       </c>
       <c r="F337" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
@@ -24631,16 +24631,16 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D338" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E338" t="n">
         <v>0.9</v>
       </c>
       <c r="F338" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
@@ -24707,13 +24707,13 @@
         <v>0.9</v>
       </c>
       <c r="D339" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="E339" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F339" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
@@ -24780,13 +24780,13 @@
         <v>0.6</v>
       </c>
       <c r="D340" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E340" t="n">
         <v>1</v>
       </c>
       <c r="F340" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>0.4</v>
       </c>
       <c r="F341" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>0.7</v>
       </c>
       <c r="F342" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -24996,16 +24996,16 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D343" t="n">
         <v>1</v>
       </c>
       <c r="E343" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F343" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>0.8</v>
       </c>
       <c r="E345" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F345" t="n">
         <v>0.5</v>
@@ -25221,7 +25221,7 @@
         <v>0.7</v>
       </c>
       <c r="E346" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F346" t="n">
         <v>0.8</v>
@@ -25294,7 +25294,7 @@
         <v>1</v>
       </c>
       <c r="E347" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F347" t="n">
         <v>0.5</v>
@@ -25367,10 +25367,10 @@
         <v>1</v>
       </c>
       <c r="E348" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F348" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
@@ -25440,10 +25440,10 @@
         <v>1</v>
       </c>
       <c r="E349" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F349" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
@@ -25507,13 +25507,13 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D350" t="n">
         <v>0.3</v>
       </c>
       <c r="E350" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F350" t="n">
         <v>0.8</v>
@@ -25653,16 +25653,16 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D352" t="n">
         <v>0.3</v>
       </c>
       <c r="E352" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F352" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G352" t="inlineStr">
         <is>
@@ -25732,10 +25732,10 @@
         <v>1</v>
       </c>
       <c r="E353" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F353" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G353" t="inlineStr">
         <is>
@@ -25799,16 +25799,16 @@
         </is>
       </c>
       <c r="C354" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D354" t="n">
+        <v>1</v>
+      </c>
+      <c r="E354" t="n">
         <v>0.8</v>
       </c>
-      <c r="D354" t="n">
+      <c r="F354" t="n">
         <v>0.8</v>
-      </c>
-      <c r="E354" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F354" t="n">
-        <v>0.9</v>
       </c>
       <c r="G354" t="inlineStr">
         <is>
@@ -25872,16 +25872,16 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D355" t="n">
         <v>1</v>
       </c>
       <c r="E355" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F355" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
@@ -26091,13 +26091,13 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D358" t="n">
         <v>1</v>
       </c>
       <c r="E358" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F358" t="n">
         <v>0.6</v>
@@ -26237,7 +26237,7 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D360" t="n">
         <v>0.3</v>
@@ -26310,16 +26310,16 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D361" t="n">
         <v>0.3</v>
       </c>
       <c r="E361" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F361" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G361" t="inlineStr">
         <is>
@@ -26386,13 +26386,13 @@
         <v>0.8</v>
       </c>
       <c r="D362" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E362" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F362" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F362" t="n">
-        <v>0.7</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
@@ -26462,10 +26462,10 @@
         <v>0.7</v>
       </c>
       <c r="E363" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F363" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F363" t="n">
-        <v>0.4</v>
       </c>
       <c r="G363" t="inlineStr">
         <is>
@@ -26602,16 +26602,16 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D365" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E365" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F365" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G365" t="inlineStr">
         <is>
@@ -26675,16 +26675,16 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="D366" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="E366" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="F366" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
@@ -26751,13 +26751,13 @@
         <v>0.3</v>
       </c>
       <c r="D367" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E367" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F367" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="G367" t="inlineStr">
         <is>
@@ -26824,13 +26824,13 @@
         <v>0.9</v>
       </c>
       <c r="D368" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E368" t="n">
         <v>0.6</v>
       </c>
       <c r="F368" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G368" t="inlineStr">
         <is>
@@ -26894,16 +26894,16 @@
         </is>
       </c>
       <c r="C369" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D369" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E369" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F369" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D369" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E369" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F369" t="n">
-        <v>0.9</v>
       </c>
       <c r="G369" t="inlineStr">
         <is>
@@ -26967,16 +26967,16 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="D370" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E370" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F370" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
@@ -27043,13 +27043,13 @@
         <v>0.8</v>
       </c>
       <c r="D371" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E371" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F371" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
@@ -27113,13 +27113,13 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D372" t="n">
         <v>0.3</v>
       </c>
       <c r="E372" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F372" t="n">
         <v>0.8</v>
@@ -27186,16 +27186,16 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D373" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E373" t="n">
         <v>0.6</v>
       </c>
       <c r="F373" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G373" t="inlineStr">
         <is>
@@ -27259,16 +27259,16 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="D374" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E374" t="n">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
       <c r="F374" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G374" t="inlineStr">
         <is>
@@ -27332,16 +27332,16 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="D375" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="E375" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F375" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>
@@ -27411,10 +27411,10 @@
         <v>1</v>
       </c>
       <c r="E376" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F376" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G376" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D378" t="n">
         <v>0.7</v>
@@ -27560,7 +27560,7 @@
         <v>0.6</v>
       </c>
       <c r="F378" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G378" t="inlineStr">
         <is>
@@ -27630,10 +27630,10 @@
         <v>0.7</v>
       </c>
       <c r="E379" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F379" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G379" t="inlineStr">
         <is>
@@ -27770,16 +27770,16 @@
         </is>
       </c>
       <c r="C381" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D381" t="n">
+        <v>1</v>
+      </c>
+      <c r="E381" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F381" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D381" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E381" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F381" t="n">
-        <v>0.9</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
@@ -27843,16 +27843,16 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D382" t="n">
         <v>1</v>
       </c>
       <c r="E382" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F382" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G382" t="inlineStr">
         <is>
@@ -27922,10 +27922,10 @@
         <v>0.2</v>
       </c>
       <c r="E383" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F383" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -27995,10 +27995,10 @@
         <v>0.2</v>
       </c>
       <c r="E384" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F384" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>0.7</v>
       </c>
       <c r="F386" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G386" t="inlineStr">
         <is>
@@ -28281,13 +28281,13 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D388" t="n">
         <v>0.7</v>
       </c>
       <c r="E388" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F388" t="n">
         <v>0.5</v>
@@ -28436,7 +28436,7 @@
         <v>0.4</v>
       </c>
       <c r="F390" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G390" t="inlineStr">
         <is>
@@ -28500,16 +28500,16 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D391" t="n">
         <v>1</v>
       </c>
       <c r="E391" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F391" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="G391" t="inlineStr">
         <is>
@@ -28646,10 +28646,10 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="D393" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E393" t="n">
         <v>0.4</v>
@@ -28719,16 +28719,16 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D394" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E394" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="F394" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G394" t="inlineStr">
         <is>
@@ -28795,13 +28795,13 @@
         <v>0.9</v>
       </c>
       <c r="D395" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E395" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F395" t="n">
         <v>0.4</v>
-      </c>
-      <c r="F395" t="n">
-        <v>0.6</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>
@@ -28865,16 +28865,16 @@
         </is>
       </c>
       <c r="C396" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D396" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E396" t="n">
         <v>0.8</v>
       </c>
-      <c r="D396" t="n">
+      <c r="F396" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E396" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F396" t="n">
-        <v>0.8</v>
       </c>
       <c r="G396" t="inlineStr">
         <is>
@@ -28938,16 +28938,16 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D397" t="n">
         <v>0.7</v>
       </c>
       <c r="E397" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F397" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G397" t="inlineStr">
         <is>
@@ -29014,13 +29014,13 @@
         <v>0.9</v>
       </c>
       <c r="D398" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E398" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F398" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
@@ -29084,16 +29084,16 @@
         </is>
       </c>
       <c r="C399" t="n">
+        <v>1</v>
+      </c>
+      <c r="D399" t="n">
+        <v>1</v>
+      </c>
+      <c r="E399" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F399" t="n">
         <v>0.8</v>
-      </c>
-      <c r="D399" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E399" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F399" t="n">
-        <v>0.7</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
@@ -29163,10 +29163,10 @@
         <v>1</v>
       </c>
       <c r="E400" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F400" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
@@ -29303,16 +29303,16 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="D402" t="n">
         <v>0.3</v>
       </c>
       <c r="E402" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F402" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F402" t="n">
-        <v>0.8</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
@@ -29376,16 +29376,16 @@
         </is>
       </c>
       <c r="C403" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D403" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E403" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F403" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D403" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E403" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F403" t="n">
-        <v>0.1</v>
       </c>
       <c r="G403" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D404" t="n">
         <v>0.7</v>
@@ -29522,7 +29522,7 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D405" t="n">
         <v>0.7</v>
@@ -29598,10 +29598,10 @@
         <v>0.6</v>
       </c>
       <c r="D406" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E406" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F406" t="n">
         <v>0.8</v>
@@ -29743,16 +29743,16 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="D408" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="E408" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="F408" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G408" t="inlineStr">
         <is>
@@ -29893,16 +29893,16 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D410" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E410" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F410" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G410" t="inlineStr">
         <is>
@@ -29971,10 +29971,10 @@
         <v>0.95</v>
       </c>
       <c r="D411" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="E411" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F411" t="n">
         <v>0.4</v>
@@ -30043,16 +30043,16 @@
         </is>
       </c>
       <c r="C412" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D412" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E412" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F412" t="n">
         <v>0.85</v>
-      </c>
-      <c r="D412" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E412" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F412" t="n">
-        <v>0.75</v>
       </c>
       <c r="G412" t="inlineStr">
         <is>
@@ -30118,16 +30118,16 @@
         </is>
       </c>
       <c r="C413" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D413" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E413" t="n">
+        <v>1</v>
+      </c>
+      <c r="F413" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D413" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E413" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F413" t="n">
-        <v>0.5</v>
       </c>
       <c r="G413" t="inlineStr">
         <is>
@@ -30343,13 +30343,13 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D416" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E416" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F416" t="n">
         <v>0.4</v>
@@ -30418,10 +30418,10 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="D417" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="E417" t="n">
         <v>0.7</v>
@@ -30493,16 +30493,16 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="D418" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="E418" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="F418" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
@@ -30568,16 +30568,16 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D419" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E419" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F419" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G419" t="inlineStr">
         <is>
@@ -30643,16 +30643,16 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D420" t="n">
         <v>0.9</v>
       </c>
       <c r="E420" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F420" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
@@ -30718,10 +30718,10 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="D421" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="E421" t="n">
         <v>0.8</v>
@@ -30793,16 +30793,16 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="D422" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="E422" t="n">
         <v>0.8</v>
       </c>
       <c r="F422" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
@@ -30874,10 +30874,10 @@
         <v>0.65</v>
       </c>
       <c r="E423" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="F423" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G423" t="inlineStr">
         <is>
@@ -30943,16 +30943,16 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D424" t="n">
         <v>0.5</v>
       </c>
       <c r="E424" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="F424" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
@@ -31093,13 +31093,13 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="D426" t="n">
         <v>0.9</v>
       </c>
       <c r="E426" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F426" t="n">
         <v>0.3</v>
@@ -31177,7 +31177,7 @@
         <v>0.8</v>
       </c>
       <c r="F427" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G427" t="inlineStr">
         <is>
@@ -31243,16 +31243,16 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="D428" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="E428" t="n">
         <v>0.4</v>
       </c>
       <c r="F428" t="n">
-        <v>0.7</v>
+        <v>0.15</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
@@ -31318,16 +31318,16 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="D429" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E429" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F429" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="G429" t="inlineStr">
         <is>
@@ -31393,13 +31393,13 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D430" t="n">
         <v>0.6</v>
       </c>
       <c r="E430" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F430" t="n">
         <v>0.7</v>
@@ -31468,16 +31468,16 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D431" t="n">
         <v>0.5</v>
       </c>
       <c r="E431" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F431" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F431" t="n">
-        <v>0.6</v>
       </c>
       <c r="G431" t="inlineStr">
         <is>
@@ -31549,10 +31549,10 @@
         <v>0.85</v>
       </c>
       <c r="E432" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F432" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
@@ -31618,16 +31618,16 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D433" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E433" t="n">
         <v>0.9</v>
       </c>
       <c r="F433" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D434" t="n">
         <v>0.4</v>
@@ -31702,7 +31702,7 @@
         <v>0.9</v>
       </c>
       <c r="F434" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
@@ -31771,13 +31771,13 @@
         <v>0.3</v>
       </c>
       <c r="D435" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E435" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F435" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G435" t="inlineStr">
         <is>
@@ -31843,16 +31843,16 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D436" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E436" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F436" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
@@ -31921,13 +31921,13 @@
         <v>0.4</v>
       </c>
       <c r="D437" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E437" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F437" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="G437" t="inlineStr">
         <is>
@@ -31996,13 +31996,13 @@
         <v>0.2</v>
       </c>
       <c r="D438" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E438" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F438" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="G438" t="inlineStr">
         <is>
@@ -32068,7 +32068,7 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D439" t="n">
         <v>0.3</v>
@@ -32077,7 +32077,7 @@
         <v>0.9</v>
       </c>
       <c r="F439" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
@@ -32143,10 +32143,10 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D440" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E440" t="n">
         <v>0.9</v>
@@ -32221,13 +32221,13 @@
         <v>0.2</v>
       </c>
       <c r="D441" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E441" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F441" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="G441" t="inlineStr">
         <is>
@@ -32293,16 +32293,16 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D442" t="n">
         <v>0.7</v>
       </c>
       <c r="E442" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F442" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>0.5</v>
       </c>
       <c r="E443" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F443" t="n">
         <v>0.8</v>
@@ -32443,16 +32443,16 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="D444" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E444" t="n">
         <v>0.8</v>
       </c>
       <c r="F444" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>0.5</v>
       </c>
       <c r="E445" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="F445" t="n">
         <v>0.4</v>
@@ -32593,16 +32593,16 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D446" t="n">
         <v>0.3</v>
       </c>
       <c r="E446" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="F446" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
@@ -32668,16 +32668,16 @@
         </is>
       </c>
       <c r="C447" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D447" t="n">
         <v>0.4</v>
       </c>
-      <c r="D447" t="n">
-        <v>0.3</v>
-      </c>
       <c r="E447" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="F447" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G447" t="inlineStr">
         <is>
@@ -32746,13 +32746,13 @@
         <v>0.4</v>
       </c>
       <c r="D448" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E448" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F448" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
@@ -32818,16 +32818,16 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D449" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E449" t="n">
         <v>0.9</v>
       </c>
       <c r="F449" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="G449" t="inlineStr">
         <is>
@@ -32893,16 +32893,16 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D450" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E450" t="n">
         <v>0.9</v>
       </c>
       <c r="F450" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>0.9</v>
       </c>
       <c r="F451" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
@@ -33043,16 +33043,16 @@
         </is>
       </c>
       <c r="C452" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D452" t="n">
         <v>0.4</v>
-      </c>
-      <c r="D452" t="n">
-        <v>0.3</v>
       </c>
       <c r="E452" t="n">
         <v>0.9</v>
       </c>
       <c r="F452" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
@@ -33118,16 +33118,16 @@
         </is>
       </c>
       <c r="C453" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D453" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E453" t="n">
         <v>0.3</v>
       </c>
-      <c r="D453" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E453" t="n">
-        <v>0.9</v>
-      </c>
       <c r="F453" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
@@ -33193,16 +33193,16 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="D454" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E454" t="n">
         <v>0.9</v>
       </c>
       <c r="F454" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
@@ -33268,16 +33268,16 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D455" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E455" t="n">
         <v>0.95</v>
       </c>
       <c r="F455" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="G455" t="inlineStr">
         <is>
@@ -33343,16 +33343,16 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D456" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="E456" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F456" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>0.7</v>
       </c>
       <c r="E457" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F457" t="n">
         <v>0.8</v>
@@ -33574,10 +33574,10 @@
         <v>0.4</v>
       </c>
       <c r="E459" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F459" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
@@ -33643,16 +33643,16 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D460" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E460" t="n">
         <v>0.9</v>
       </c>
       <c r="F460" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>0.3</v>
       </c>
       <c r="F461" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G461" t="inlineStr">
         <is>
@@ -33799,10 +33799,10 @@
         <v>1</v>
       </c>
       <c r="E462" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F462" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
@@ -33868,13 +33868,13 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="D463" t="n">
         <v>0.9</v>
       </c>
       <c r="E463" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F463" t="n">
         <v>0.3</v>
@@ -33952,7 +33952,7 @@
         <v>0.5</v>
       </c>
       <c r="F464" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D465" t="n">
         <v>0.8</v>
@@ -34099,7 +34099,7 @@
         <v>0.6</v>
       </c>
       <c r="E466" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F466" t="n">
         <v>0.5</v>
@@ -34168,16 +34168,16 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="D467" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="E467" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="F467" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="G467" t="inlineStr">
         <is>
@@ -34243,16 +34243,16 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D468" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E468" t="n">
         <v>0.9</v>
       </c>
       <c r="F468" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
@@ -34318,16 +34318,16 @@
         </is>
       </c>
       <c r="C469" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D469" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E469" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F469" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D469" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E469" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F469" t="n">
-        <v>0.5</v>
       </c>
       <c r="G469" t="inlineStr">
         <is>
@@ -34399,10 +34399,10 @@
         <v>0.5</v>
       </c>
       <c r="E470" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F470" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
@@ -34468,16 +34468,16 @@
         </is>
       </c>
       <c r="C471" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D471" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E471" t="n">
         <v>0.8</v>
       </c>
-      <c r="D471" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E471" t="n">
-        <v>0.7</v>
-      </c>
       <c r="F471" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G471" t="inlineStr">
         <is>
@@ -34543,16 +34543,16 @@
         </is>
       </c>
       <c r="C472" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D472" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E472" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F472" t="n">
         <v>0.8</v>
-      </c>
-      <c r="D472" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E472" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F472" t="n">
-        <v>0.85</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
@@ -34618,13 +34618,13 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D473" t="n">
         <v>0.4</v>
       </c>
       <c r="E473" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F473" t="n">
         <v>0.6</v>
@@ -34693,16 +34693,16 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D474" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E474" t="n">
         <v>0.8</v>
       </c>
       <c r="F474" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
@@ -34846,13 +34846,13 @@
         <v>0.6</v>
       </c>
       <c r="D476" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E476" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F476" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
@@ -34918,16 +34918,16 @@
         </is>
       </c>
       <c r="C477" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D477" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E477" t="n">
         <v>0.6</v>
       </c>
-      <c r="D477" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E477" t="n">
-        <v>0.5</v>
-      </c>
       <c r="F477" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>0.8</v>
       </c>
       <c r="F478" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D479" t="n">
         <v>0.5</v>
@@ -35077,7 +35077,7 @@
         <v>0.9</v>
       </c>
       <c r="F479" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G479" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>0.6</v>
       </c>
       <c r="F480" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
@@ -35218,16 +35218,16 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D481" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E481" t="n">
         <v>0.8</v>
       </c>
       <c r="F481" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
@@ -35293,16 +35293,16 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D482" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E482" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F482" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
@@ -35368,16 +35368,16 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="D483" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="E483" t="n">
         <v>0.4</v>
       </c>
       <c r="F483" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G483" t="inlineStr">
         <is>
@@ -35446,13 +35446,13 @@
         <v>0.75</v>
       </c>
       <c r="D484" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="E484" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="F484" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
@@ -35593,16 +35593,16 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D486" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E486" t="n">
         <v>0.9</v>
       </c>
       <c r="F486" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>0.6</v>
       </c>
       <c r="F487" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
@@ -35743,16 +35743,16 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D488" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E488" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F488" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F488" t="n">
-        <v>0.6</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
@@ -35818,16 +35818,16 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D489" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E489" t="n">
         <v>0.9</v>
       </c>
       <c r="F489" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="G489" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>0.9</v>
       </c>
       <c r="F491" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="G491" t="inlineStr">
         <is>
@@ -36043,16 +36043,16 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="D492" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="E492" t="n">
         <v>0.4</v>
       </c>
       <c r="F492" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
@@ -36118,16 +36118,16 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D493" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E493" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F493" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G493" t="inlineStr">
         <is>
@@ -36196,13 +36196,13 @@
         <v>0.75</v>
       </c>
       <c r="D494" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="E494" t="n">
         <v>0.9</v>
       </c>
       <c r="F494" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
@@ -36268,16 +36268,16 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D495" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E495" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="F495" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
@@ -36346,13 +36346,13 @@
         <v>0.85</v>
       </c>
       <c r="D496" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="E496" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F496" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
@@ -36418,16 +36418,16 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D497" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E497" t="n">
         <v>0.9</v>
       </c>
       <c r="F497" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
@@ -36568,16 +36568,16 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="D499" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="E499" t="n">
         <v>0.9</v>
       </c>
       <c r="F499" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="G499" t="inlineStr">
         <is>
@@ -36643,10 +36643,10 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D500" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E500" t="n">
         <v>0.8</v>
@@ -36724,7 +36724,7 @@
         <v>0.8</v>
       </c>
       <c r="E501" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="F501" t="n">
         <v>0.3</v>
@@ -36868,16 +36868,16 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="D503" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="E503" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F503" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>0.9</v>
       </c>
       <c r="E504" t="n">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="F504" t="n">
         <v>0.3</v>
@@ -37018,7 +37018,7 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="D505" t="n">
         <v>0.7</v>
@@ -37027,7 +37027,7 @@
         <v>0.95</v>
       </c>
       <c r="F505" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="G505" t="inlineStr">
         <is>
@@ -37093,10 +37093,10 @@
         </is>
       </c>
       <c r="C506" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D506" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E506" t="n">
         <v>0.8</v>
@@ -37243,10 +37243,10 @@
         </is>
       </c>
       <c r="C508" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="D508" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="E508" t="n">
         <v>0.9</v>
@@ -37318,16 +37318,16 @@
         </is>
       </c>
       <c r="C509" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="D509" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E509" t="n">
         <v>0.8</v>
       </c>
       <c r="F509" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G509" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>0.5</v>
       </c>
       <c r="E512" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F512" t="n">
         <v>0.4</v>
@@ -37627,7 +37627,7 @@
         <v>0.75</v>
       </c>
       <c r="F513" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="G513" t="inlineStr">
         <is>
@@ -37699,10 +37699,10 @@
         <v>0.55</v>
       </c>
       <c r="E514" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F514" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="G514" t="inlineStr">
         <is>
@@ -37768,16 +37768,16 @@
         </is>
       </c>
       <c r="C515" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="D515" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E515" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F515" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G515" t="inlineStr">
         <is>
@@ -37843,16 +37843,16 @@
         </is>
       </c>
       <c r="C516" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D516" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E516" t="n">
         <v>0.8</v>
       </c>
       <c r="F516" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
@@ -37918,16 +37918,16 @@
         </is>
       </c>
       <c r="C517" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="D517" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="E517" t="n">
         <v>0.9</v>
       </c>
       <c r="F517" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="G517" t="inlineStr">
         <is>
@@ -37993,16 +37993,16 @@
         </is>
       </c>
       <c r="C518" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="D518" t="n">
         <v>0.5</v>
       </c>
       <c r="E518" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="F518" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G518" t="inlineStr">
         <is>
@@ -38143,16 +38143,16 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="D520" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="E520" t="n">
         <v>0.9</v>
       </c>
       <c r="F520" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="G520" t="inlineStr">
         <is>
@@ -38218,16 +38218,16 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D521" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E521" t="n">
         <v>0.9</v>
       </c>
       <c r="F521" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
@@ -38299,10 +38299,10 @@
         <v>0.4</v>
       </c>
       <c r="E522" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="F522" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         </is>
       </c>
       <c r="C523" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="D523" t="n">
         <v>0.7</v>
@@ -38377,7 +38377,7 @@
         <v>0.9</v>
       </c>
       <c r="F523" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="G523" t="inlineStr">
         <is>
@@ -38443,16 +38443,16 @@
         </is>
       </c>
       <c r="C524" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D524" t="n">
         <v>0.5</v>
       </c>
       <c r="E524" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F524" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
@@ -38518,16 +38518,16 @@
         </is>
       </c>
       <c r="C525" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D525" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E525" t="n">
         <v>0.8</v>
       </c>
       <c r="F525" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
@@ -38593,16 +38593,16 @@
         </is>
       </c>
       <c r="C526" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D526" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E526" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F526" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
@@ -38668,13 +38668,13 @@
         </is>
       </c>
       <c r="C527" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D527" t="n">
         <v>0.4</v>
       </c>
       <c r="E527" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F527" t="n">
         <v>0.6</v>
@@ -38743,10 +38743,10 @@
         </is>
       </c>
       <c r="C528" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="D528" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="E528" t="n">
         <v>0.7</v>
@@ -38818,16 +38818,16 @@
         </is>
       </c>
       <c r="C529" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="D529" t="n">
         <v>0.6</v>
       </c>
       <c r="E529" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="F529" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G529" t="inlineStr">
         <is>
@@ -38899,10 +38899,10 @@
         <v>0.6</v>
       </c>
       <c r="E530" t="n">
+        <v>1</v>
+      </c>
+      <c r="F530" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F530" t="n">
-        <v>0.5</v>
       </c>
       <c r="G530" t="inlineStr">
         <is>
@@ -39043,10 +39043,10 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="D532" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="E532" t="n">
         <v>0.9</v>
@@ -39118,13 +39118,13 @@
         </is>
       </c>
       <c r="C533" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D533" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E533" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F533" t="n">
         <v>0.6</v>
@@ -39193,7 +39193,7 @@
         </is>
       </c>
       <c r="C534" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D534" t="n">
         <v>0.8</v>
@@ -39268,10 +39268,10 @@
         </is>
       </c>
       <c r="C535" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="D535" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="E535" t="n">
         <v>0.9</v>
@@ -39343,10 +39343,10 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D536" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E536" t="n">
         <v>0.9</v>
@@ -39493,10 +39493,10 @@
         </is>
       </c>
       <c r="C538" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D538" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E538" t="n">
         <v>0.9</v>
@@ -39577,7 +39577,7 @@
         <v>0.9</v>
       </c>
       <c r="F539" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G539" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>0.6</v>
       </c>
       <c r="F540" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="G540" t="inlineStr">
         <is>
@@ -39718,7 +39718,7 @@
         </is>
       </c>
       <c r="C541" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="D541" t="n">
         <v>0.7</v>
@@ -39793,10 +39793,10 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D542" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E542" t="n">
         <v>0.9</v>
@@ -39868,16 +39868,16 @@
         </is>
       </c>
       <c r="C543" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D543" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E543" t="n">
         <v>0.4</v>
       </c>
-      <c r="D543" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E543" t="n">
-        <v>0.3</v>
-      </c>
       <c r="F543" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="G543" t="inlineStr">
         <is>
@@ -39943,16 +39943,16 @@
         </is>
       </c>
       <c r="C544" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D544" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E544" t="n">
         <v>0.8</v>
       </c>
       <c r="F544" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G544" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>0.3</v>
       </c>
       <c r="F545" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="G545" t="inlineStr">
         <is>
@@ -40093,16 +40093,16 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="D546" t="n">
         <v>0.5</v>
       </c>
       <c r="E546" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="F546" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G546" t="inlineStr">
         <is>
@@ -40171,10 +40171,10 @@
         <v>0.85</v>
       </c>
       <c r="D547" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E547" t="n">
         <v>0.8</v>
-      </c>
-      <c r="E547" t="n">
-        <v>0.85</v>
       </c>
       <c r="F547" t="n">
         <v>0.7</v>
@@ -40318,10 +40318,10 @@
         </is>
       </c>
       <c r="C549" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D549" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E549" t="n">
         <v>0.95</v>
@@ -40468,16 +40468,16 @@
         </is>
       </c>
       <c r="C551" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D551" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E551" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F551" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D551" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E551" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F551" t="n">
-        <v>0.4</v>
       </c>
       <c r="G551" t="inlineStr">
         <is>
@@ -40543,16 +40543,16 @@
         </is>
       </c>
       <c r="C552" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D552" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E552" t="n">
         <v>0.8</v>
       </c>
-      <c r="D552" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E552" t="n">
-        <v>0.7</v>
-      </c>
       <c r="F552" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="G552" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         </is>
       </c>
       <c r="C553" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="D553" t="n">
         <v>0.7</v>
@@ -40627,7 +40627,7 @@
         <v>0.95</v>
       </c>
       <c r="F553" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="G553" t="inlineStr">
         <is>
@@ -40696,13 +40696,13 @@
         <v>0.5</v>
       </c>
       <c r="D554" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E554" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="F554" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="G554" t="inlineStr">
         <is>
@@ -40843,10 +40843,10 @@
         </is>
       </c>
       <c r="C556" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="D556" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="E556" t="n">
         <v>0.9</v>
@@ -40993,13 +40993,13 @@
         </is>
       </c>
       <c r="C558" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D558" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E558" t="n">
         <v>0.85</v>
-      </c>
-      <c r="D558" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E558" t="n">
-        <v>0.8</v>
       </c>
       <c r="F558" t="n">
         <v>0.4</v>
@@ -41068,16 +41068,16 @@
         </is>
       </c>
       <c r="C559" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="D559" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="E559" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F559" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="G559" t="inlineStr">
         <is>
@@ -41146,13 +41146,13 @@
         <v>0.4</v>
       </c>
       <c r="D560" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E560" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F560" t="n">
         <v>0.4</v>
-      </c>
-      <c r="E560" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F560" t="n">
-        <v>0.3</v>
       </c>
       <c r="G560" t="inlineStr">
         <is>
@@ -41218,16 +41218,16 @@
         </is>
       </c>
       <c r="C561" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D561" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E561" t="n">
         <v>0.8</v>
       </c>
       <c r="F561" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G561" t="inlineStr">
         <is>
@@ -41293,10 +41293,10 @@
         </is>
       </c>
       <c r="C562" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="D562" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E562" t="n">
         <v>0.9</v>
@@ -41374,10 +41374,10 @@
         <v>0.5</v>
       </c>
       <c r="E563" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F563" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="G563" t="inlineStr">
         <is>
@@ -41443,13 +41443,13 @@
         </is>
       </c>
       <c r="C564" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D564" t="n">
         <v>0.8</v>
       </c>
-      <c r="D564" t="n">
-        <v>0.9</v>
-      </c>
       <c r="E564" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F564" t="n">
         <v>0.3</v>
@@ -41668,7 +41668,7 @@
         </is>
       </c>
       <c r="C567" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="D567" t="n">
         <v>0.9</v>
@@ -41749,7 +41749,7 @@
         <v>0.7</v>
       </c>
       <c r="E568" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F568" t="n">
         <v>0.8</v>
@@ -41974,7 +41974,7 @@
         <v>0.65</v>
       </c>
       <c r="E571" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F571" t="n">
         <v>0.55</v>
@@ -42043,16 +42043,16 @@
         </is>
       </c>
       <c r="C572" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D572" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E572" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F572" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G572" t="inlineStr">
         <is>
@@ -42124,7 +42124,7 @@
         <v>0.8</v>
       </c>
       <c r="E573" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="F573" t="n">
         <v>0.3</v>
@@ -42196,7 +42196,7 @@
         <v>0.7</v>
       </c>
       <c r="D574" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E574" t="n">
         <v>0.9</v>
@@ -42424,7 +42424,7 @@
         <v>0.7</v>
       </c>
       <c r="E577" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F577" t="n">
         <v>0.8</v>
@@ -42493,16 +42493,16 @@
         </is>
       </c>
       <c r="C578" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="D578" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E578" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="F578" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="G578" t="inlineStr">
         <is>
@@ -42718,10 +42718,10 @@
         </is>
       </c>
       <c r="C581" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="D581" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="E581" t="n">
         <v>0.8</v>
@@ -43018,13 +43018,13 @@
         </is>
       </c>
       <c r="C585" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="D585" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="E585" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="F585" t="n">
         <v>0.3</v>
